--- a/IAG Solar Flux Atlas/Infrared range/Data/Values_NIR.xlsx
+++ b/IAG Solar Flux Atlas/Infrared range/Data/Values_NIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Emitted wavelength</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Bisector slope</t>
-  </si>
-  <si>
-    <t>Blueshift</t>
   </si>
   <si>
     <t>Line Depth</t>
@@ -395,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,11 +417,8 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>10035.6094</v>
       </c>
@@ -441,16 +435,13 @@
         <v>1092414854.350568</v>
       </c>
       <c r="F2">
-        <v>156677110.1056063</v>
+        <v>5244.799639624118</v>
       </c>
       <c r="G2">
-        <v>209.110092138397</v>
-      </c>
-      <c r="H2">
         <v>0.05743405427202564</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>10084.1584</v>
       </c>
@@ -467,16 +458,13 @@
         <v>1039916995.203525</v>
       </c>
       <c r="F3">
-        <v>95784039.45845836</v>
+        <v>3221.903579408068</v>
       </c>
       <c r="G3">
-        <v>300.2634136864436</v>
-      </c>
-      <c r="H3">
         <v>0.04336456425362079</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>10116.7892</v>
       </c>
@@ -493,16 +481,13 @@
         <v>2487722571.704799</v>
       </c>
       <c r="F4">
-        <v>62683098.96488434</v>
+        <v>2115.304006609283</v>
       </c>
       <c r="G4">
-        <v>231.1386673049972</v>
-      </c>
-      <c r="H4">
         <v>0.1078840065190858</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>10139.8807</v>
       </c>
@@ -519,16 +504,13 @@
         <v>1164347933.249144</v>
       </c>
       <c r="F5">
-        <v>166611754.3473985</v>
+        <v>5635.310586103822</v>
       </c>
       <c r="G5">
-        <v>53.21822221639219</v>
-      </c>
-      <c r="H5">
         <v>0.05441244081384189</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>10145.6242</v>
       </c>
@@ -545,16 +527,13 @@
         <v>1427904249.565825</v>
       </c>
       <c r="F6">
-        <v>-22663026.0553909</v>
+        <v>-766.9660841715427</v>
       </c>
       <c r="G6">
-        <v>132.9702376056558</v>
-      </c>
-      <c r="H6">
         <v>0.08342017248217437</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>10148.3444</v>
       </c>
@@ -571,16 +550,13 @@
         <v>4861451483.351841</v>
       </c>
       <c r="F7">
-        <v>-28409543.72762407</v>
+        <v>-961.6992736824802</v>
       </c>
       <c r="G7">
-        <v>369.2627661837664</v>
-      </c>
-      <c r="H7">
         <v>0.421270623771574</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>10157.949</v>
       </c>
@@ -597,16 +573,13 @@
         <v>2369787863.916452</v>
       </c>
       <c r="F8">
-        <v>45429471.48641107</v>
+        <v>1539.300215407534</v>
       </c>
       <c r="G8">
-        <v>221.3481712655098</v>
-      </c>
-      <c r="H8">
         <v>0.1077095019960794</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>10170.2562</v>
       </c>
@@ -623,16 +596,13 @@
         <v>2893465557.268535</v>
       </c>
       <c r="F9">
-        <v>52285354.05180201</v>
+        <v>1773.746446228068</v>
       </c>
       <c r="G9">
-        <v>203.3938889715005</v>
-      </c>
-      <c r="H9">
         <v>0.1272931818998715</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>10219.1142</v>
       </c>
@@ -649,16 +619,13 @@
         <v>4898282972.106872</v>
       </c>
       <c r="F10">
-        <v>-7300468.186603961</v>
+        <v>-248.8535839663971</v>
       </c>
       <c r="G10">
-        <v>440.04664022485</v>
-      </c>
-      <c r="H10">
         <v>0.4473702354949702</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10221.2115</v>
       </c>
@@ -675,16 +642,13 @@
         <v>4769684636.022537</v>
       </c>
       <c r="F11">
-        <v>3783279.059394291</v>
+        <v>128.9883042273192</v>
       </c>
       <c r="G11">
-        <v>196.5138348174656</v>
-      </c>
-      <c r="H11">
         <v>0.2298472183399822</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>10268.0337</v>
       </c>
@@ -701,16 +665,13 @@
         <v>1175894603.604178</v>
       </c>
       <c r="F12">
-        <v>101648915.6019635</v>
+        <v>3481.525409833173</v>
       </c>
       <c r="G12">
-        <v>163.5013882968728</v>
-      </c>
-      <c r="H12">
         <v>0.05221142329858397</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>10310.2796</v>
       </c>
@@ -727,16 +688,13 @@
         <v>651237286.9919277</v>
       </c>
       <c r="F13">
-        <v>406184614.3090176</v>
+        <v>13969.25640635996</v>
       </c>
       <c r="G13">
-        <v>55.24638439732712</v>
-      </c>
-      <c r="H13">
         <v>0.0381781167068026</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>10335.161</v>
       </c>
@@ -753,16 +711,13 @@
         <v>1483377073.555127</v>
       </c>
       <c r="F14">
-        <v>87995685.52016665</v>
+        <v>3033.599689557504</v>
       </c>
       <c r="G14">
-        <v>240.7584556362024</v>
-      </c>
-      <c r="H14">
         <v>0.06757830636614381</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>10343.7208</v>
       </c>
@@ -779,16 +734,13 @@
         <v>5741618897.409628</v>
       </c>
       <c r="F15">
-        <v>3332097.627462617</v>
+        <v>114.9672501994914</v>
       </c>
       <c r="G15">
-        <v>234.7626117048913</v>
-      </c>
-      <c r="H15">
         <v>0.2723157778789259</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>10348.0194</v>
       </c>
@@ -805,16 +757,13 @@
         <v>816452194.0869088</v>
       </c>
       <c r="F16">
-        <v>24187923.80759507</v>
+        <v>834.9014907977103</v>
       </c>
       <c r="G16">
-        <v>78.22169691553601</v>
-      </c>
-      <c r="H16">
         <v>0.04586915356115895</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>10350.8021</v>
       </c>
@@ -831,16 +780,13 @@
         <v>3023016423.668905</v>
       </c>
       <c r="F17">
-        <v>977415.4649770735</v>
+        <v>33.74681688153097</v>
       </c>
       <c r="G17">
-        <v>211.4314352049752</v>
-      </c>
-      <c r="H17">
         <v>0.1795332271979354</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>10365.544</v>
       </c>
@@ -857,16 +803,13 @@
         <v>1167710602.469932</v>
       </c>
       <c r="F18">
-        <v>101261740.0364153</v>
+        <v>3501.200716254912</v>
       </c>
       <c r="G18">
-        <v>156.1789013206684</v>
-      </c>
-      <c r="H18">
         <v>0.06653239493464458</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>10381.8464</v>
       </c>
@@ -883,16 +826,13 @@
         <v>2620537720.623078</v>
       </c>
       <c r="F19">
-        <v>8616107.045082089</v>
+        <v>298.376901502161</v>
       </c>
       <c r="G19">
-        <v>150.158336158803</v>
-      </c>
-      <c r="H19">
         <v>0.1182933865991311</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>10391.5915</v>
       </c>
@@ -909,16 +849,13 @@
         <v>912103665.3756156</v>
       </c>
       <c r="F20">
-        <v>155365542.5129987</v>
+        <v>5385.380103624098</v>
       </c>
       <c r="G20">
-        <v>201.9466609972183</v>
-      </c>
-      <c r="H20">
         <v>0.04838380501972273</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>10398.6467</v>
       </c>
@@ -935,16 +872,13 @@
         <v>6334397162.849628</v>
       </c>
       <c r="F21">
-        <v>-5619379.032977202</v>
+        <v>-194.9147914858533</v>
       </c>
       <c r="G21">
-        <v>242.1715747933119</v>
-      </c>
-      <c r="H21">
         <v>0.3273813461267876</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>10425.8871</v>
       </c>
@@ -961,16 +895,13 @@
         <v>2907342842.092541</v>
       </c>
       <c r="F22">
-        <v>23491007.64812877</v>
+        <v>816.9477985333124</v>
       </c>
       <c r="G22">
-        <v>238.6633748817404</v>
-      </c>
-      <c r="H22">
         <v>0.1372495836200107</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>10426.6023</v>
       </c>
@@ -987,16 +918,13 @@
         <v>3650308171.970758</v>
       </c>
       <c r="F23">
-        <v>-4861517.001753004</v>
+        <v>-169.0807706744947</v>
       </c>
       <c r="G23">
-        <v>209.894352961243</v>
-      </c>
-      <c r="H23">
         <v>0.1757809642438444</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>10472.5234</v>
       </c>
@@ -1013,16 +941,13 @@
         <v>5367784831.088258</v>
       </c>
       <c r="F24">
-        <v>-7306275.050283175</v>
+        <v>-255.2273954034393</v>
       </c>
       <c r="G24">
-        <v>437.9865704075818</v>
-      </c>
-      <c r="H24">
         <v>0.3844519388649174</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>10535.122</v>
       </c>
@@ -1039,16 +964,13 @@
         <v>5502191211.121552</v>
       </c>
       <c r="F25">
-        <v>3667309.38911736</v>
+        <v>128.874474444179</v>
       </c>
       <c r="G25">
-        <v>338.6320776117072</v>
-      </c>
-      <c r="H25">
         <v>0.3085268521076436</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>10558.5438</v>
       </c>
@@ -1065,16 +987,13 @@
         <v>1109103792.656712</v>
       </c>
       <c r="F26">
-        <v>25102531.12714076</v>
+        <v>884.0993591355111</v>
       </c>
       <c r="G26">
-        <v>164.6814456252225</v>
-      </c>
-      <c r="H26">
         <v>0.0670847560112463</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>10580.039</v>
       </c>
@@ -1091,16 +1010,13 @@
         <v>2276211567.059862</v>
       </c>
       <c r="F27">
-        <v>23994375.32402267</v>
+        <v>846.7913554172056</v>
       </c>
       <c r="G27">
-        <v>277.6895329283418</v>
-      </c>
-      <c r="H27">
         <v>0.1033682216932009</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>10619.6322</v>
       </c>
@@ -1117,16 +1033,13 @@
         <v>2230216978.745636</v>
       </c>
       <c r="F28">
-        <v>28263552.39839941</v>
+        <v>1001.188316653564</v>
       </c>
       <c r="G28">
-        <v>175.0261407137777</v>
-      </c>
-      <c r="H28">
         <v>0.09248573920519065</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>10755.9531</v>
       </c>
@@ -1143,16 +1056,13 @@
         <v>4012371034.929343</v>
       </c>
       <c r="F29">
-        <v>9957776.974086111</v>
+        <v>357.265401017195</v>
       </c>
       <c r="G29">
-        <v>253.6373431923298</v>
-      </c>
-      <c r="H29">
         <v>0.2048284554576423</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>10783.6477</v>
       </c>
@@ -1169,16 +1079,13 @@
         <v>1423530335.532048</v>
       </c>
       <c r="F30">
-        <v>48341681.80190385</v>
+        <v>1738.870222676047</v>
       </c>
       <c r="G30">
-        <v>294.6869318163317</v>
-      </c>
-      <c r="H30">
         <v>0.05906670278145498</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>10786.0053</v>
       </c>
@@ -1195,16 +1102,13 @@
         <v>5131435504.372919</v>
       </c>
       <c r="F31">
-        <v>8438671.782919452</v>
+        <v>303.6087781286614</v>
       </c>
       <c r="G31">
-        <v>208.4593297016262</v>
-      </c>
-      <c r="H31">
         <v>0.2490098102851527</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>10821.2401</v>
       </c>
@@ -1221,16 +1125,13 @@
         <v>3567627233.572556</v>
       </c>
       <c r="F32">
-        <v>13690480.77423065</v>
+        <v>494.1688922136092</v>
       </c>
       <c r="G32">
-        <v>257.6479066640685</v>
-      </c>
-      <c r="H32">
         <v>0.1812736686169343</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>10887.2463</v>
       </c>
@@ -1247,16 +1148,13 @@
         <v>3740177205.343518</v>
       </c>
       <c r="F33">
-        <v>5682019.626809872</v>
+        <v>206.3481014819639</v>
       </c>
       <c r="G33">
-        <v>278.1147539102653</v>
-      </c>
-      <c r="H33">
         <v>0.2007178698010487</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>10899.2871</v>
       </c>
@@ -1273,16 +1171,13 @@
         <v>4551789703.786042</v>
       </c>
       <c r="F34">
-        <v>-7373565.200082134</v>
+        <v>-268.0743398383133</v>
       </c>
       <c r="G34">
-        <v>228.2972618982217</v>
-      </c>
-      <c r="H34">
         <v>0.2228342720043448</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>11122.8432</v>
       </c>
@@ -1299,16 +1194,13 @@
         <v>5920332872.86448</v>
       </c>
       <c r="F35">
-        <v>-8343150.216613088</v>
+        <v>-309.5462881650304</v>
       </c>
       <c r="G35">
-        <v>293.786195995636</v>
-      </c>
-      <c r="H35">
         <v>0.4211667023471034</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>11672.8365</v>
       </c>
@@ -1325,16 +1217,13 @@
         <v>5053048059.109766</v>
       </c>
       <c r="F36">
-        <v>29709112.09872661</v>
+        <v>1156.766371613857</v>
       </c>
       <c r="G36">
-        <v>195.1901477600028</v>
-      </c>
-      <c r="H36">
         <v>0.2825499315196948</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>11887.3385</v>
       </c>
@@ -1351,16 +1240,13 @@
         <v>4078361117.601238</v>
       </c>
       <c r="F37">
-        <v>-33204587.71600025</v>
+        <v>-1316.626734401364</v>
       </c>
       <c r="G37">
-        <v>448.9066877308219</v>
-      </c>
-      <c r="H37">
         <v>0.5155049647336023</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>11893.7446</v>
       </c>
@@ -1377,16 +1263,13 @@
         <v>3234104353.83377</v>
       </c>
       <c r="F38">
-        <v>-7962682.93565054</v>
+        <v>-315.905772814927</v>
       </c>
       <c r="G38">
-        <v>161.3177175190825</v>
-      </c>
-      <c r="H38">
         <v>0.2668516992595176</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>12056.3824</v>
       </c>
@@ -1403,16 +1286,13 @@
         <v>3292310950.058791</v>
       </c>
       <c r="F39">
-        <v>-8322813.517383904</v>
+        <v>-334.7085335471169</v>
       </c>
       <c r="G39">
-        <v>213.8464966395116</v>
-      </c>
-      <c r="H39">
         <v>0.1780402991050559</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>12134.4953</v>
       </c>
@@ -1429,16 +1309,13 @@
         <v>484919102.1449975</v>
       </c>
       <c r="F40">
-        <v>-37658692.86906283</v>
+        <v>-1524.285019006487</v>
       </c>
       <c r="G40">
-        <v>-51.88218762412625</v>
-      </c>
-      <c r="H40">
         <v>0.0303586954027002</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>12216.6754</v>
       </c>
@@ -1455,16 +1332,13 @@
         <v>1956128998.876171</v>
       </c>
       <c r="F41">
-        <v>63107876.30689377</v>
+        <v>2571.674490646211</v>
       </c>
       <c r="G41">
-        <v>68.71090987194373</v>
-      </c>
-      <c r="H41">
         <v>0.1197162419001919</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>12230.459</v>
       </c>
@@ -1481,16 +1355,13 @@
         <v>3958370237.736347</v>
       </c>
       <c r="F42">
-        <v>7461850.332053294</v>
+        <v>304.4169959352749</v>
       </c>
       <c r="G42">
-        <v>213.2540066162134</v>
-      </c>
-      <c r="H42">
         <v>0.2292024751489307</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>12343.864</v>
       </c>
@@ -1507,16 +1378,13 @@
         <v>885320110.7129227</v>
       </c>
       <c r="F43">
-        <v>-18408945.50113069</v>
+        <v>-757.9829176020954</v>
       </c>
       <c r="G43">
-        <v>55.85954716125617</v>
-      </c>
-      <c r="H43">
         <v>0.04912497529315707</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>12346.2918</v>
       </c>
@@ -1533,16 +1401,13 @@
         <v>2893479150.314776</v>
       </c>
       <c r="F44">
-        <v>25835291.56025861</v>
+        <v>1063.970555358041</v>
       </c>
       <c r="G44">
-        <v>281.6710125485241</v>
-      </c>
-      <c r="H44">
         <v>0.1798162446270126</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>12560.4345</v>
       </c>
@@ -1559,16 +1424,13 @@
         <v>3698188201.947296</v>
       </c>
       <c r="F45">
-        <v>7148187.431506136</v>
+        <v>299.4885431884319</v>
       </c>
       <c r="G45">
-        <v>221.9724054358576</v>
-      </c>
-      <c r="H45">
         <v>0.1746831963221127</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>12619.3777</v>
       </c>
@@ -1585,16 +1447,13 @@
         <v>2922384018.712894</v>
       </c>
       <c r="F46">
-        <v>-8848614.204445509</v>
+        <v>-372.4713075647748</v>
       </c>
       <c r="G46">
-        <v>225.6869093191555</v>
-      </c>
-      <c r="H46">
         <v>0.1687032067109444</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>12642.1643</v>
       </c>
@@ -1611,16 +1470,13 @@
         <v>4279152310.849101</v>
       </c>
       <c r="F47">
-        <v>-4111393.746382472</v>
+        <v>-173.3765300139311</v>
       </c>
       <c r="G47">
-        <v>350.9627206966982</v>
-      </c>
-      <c r="H47">
         <v>0.3822909995149532</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>12810.6535</v>
       </c>
@@ -1637,16 +1493,13 @@
         <v>3337081972.08334</v>
       </c>
       <c r="F48">
-        <v>12799969.90510492</v>
+        <v>546.9656021309805</v>
       </c>
       <c r="G48">
-        <v>334.645859331857</v>
-      </c>
-      <c r="H48">
         <v>0.2053903855489194</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>12828.3694</v>
       </c>
@@ -1663,16 +1516,13 @@
         <v>2273626482.28181</v>
       </c>
       <c r="F49">
-        <v>4101617.602997416</v>
+        <v>175.5117774681683</v>
       </c>
       <c r="G49">
-        <v>236.03185496702</v>
-      </c>
-      <c r="H49">
         <v>0.1553177192869108</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>12844.0867</v>
       </c>
@@ -1689,16 +1539,13 @@
         <v>1663237571.869143</v>
       </c>
       <c r="F50">
-        <v>24495923.06465667</v>
+        <v>1049.486342761636</v>
       </c>
       <c r="G50">
-        <v>315.1020603992357</v>
-      </c>
-      <c r="H50">
         <v>0.1166086985709455</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>12883.2924</v>
       </c>
@@ -1715,16 +1562,13 @@
         <v>5652830475.671362</v>
       </c>
       <c r="F51">
-        <v>-650730.1445753785</v>
+        <v>-27.96452696127717</v>
       </c>
       <c r="G51">
-        <v>269.930418796854</v>
-      </c>
-      <c r="H51">
         <v>0.3101707375451361</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>12936.5437</v>
       </c>
@@ -1741,16 +1585,13 @@
         <v>1054536340.142622</v>
       </c>
       <c r="F52">
-        <v>215975076.2760331</v>
+        <v>9319.689458536344</v>
       </c>
       <c r="G52">
-        <v>171.488168777924</v>
-      </c>
-      <c r="H52">
         <v>0.06063908456286959</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>13355.8281</v>
       </c>
@@ -1767,16 +1608,13 @@
         <v>3940752423.939021</v>
       </c>
       <c r="F53">
-        <v>-17138920.22262292</v>
+        <v>-763.5435664254074</v>
       </c>
       <c r="G53">
-        <v>170.5938907839318</v>
-      </c>
-      <c r="H53">
         <v>0.4144432072896289</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>13395.7647</v>
       </c>
@@ -1793,16 +1631,13 @@
         <v>3645317858.151546</v>
       </c>
       <c r="F54">
-        <v>-27702535.8647331</v>
+        <v>-1237.846317028473</v>
       </c>
       <c r="G54">
-        <v>273.0316685858902</v>
-      </c>
-      <c r="H54">
         <v>0.4533664680095457</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>14812.3724</v>
       </c>
@@ -1819,16 +1654,13 @@
         <v>4176362792.286147</v>
       </c>
       <c r="F55">
-        <v>11991303.16024815</v>
+        <v>592.4753276497</v>
       </c>
       <c r="G55">
-        <v>-22.26326037205379</v>
-      </c>
-      <c r="H55">
         <v>0.4710089648712248</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>14960.2394</v>
       </c>
@@ -1845,16 +1677,13 @@
         <v>3416335965.676072</v>
       </c>
       <c r="F56">
-        <v>-4225147.812217094</v>
+        <v>-210.8434200009328</v>
       </c>
       <c r="G56">
-        <v>210.4124623500545</v>
-      </c>
-      <c r="H56">
         <v>0.438722636188979</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>15021.8064</v>
       </c>
@@ -1871,16 +1700,13 @@
         <v>2350162102.19848</v>
       </c>
       <c r="F57">
-        <v>18432425.35255145</v>
+        <v>923.600909496261</v>
       </c>
       <c r="G57">
-        <v>283.3915436144903</v>
-      </c>
-      <c r="H57">
         <v>0.2279662670300612</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>15055.8625</v>
       </c>
@@ -1897,16 +1723,13 @@
         <v>3532133521.254247</v>
       </c>
       <c r="F58">
-        <v>-19652248.51544683</v>
+        <v>-986.955760619971</v>
       </c>
       <c r="G58">
-        <v>346.4689432125126</v>
-      </c>
-      <c r="H58">
         <v>0.4620905734588536</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>15098.8248</v>
       </c>
@@ -1923,16 +1746,13 @@
         <v>3476608258.668179</v>
       </c>
       <c r="F59">
-        <v>1998760.828410971</v>
+        <v>100.6661320364879</v>
       </c>
       <c r="G59">
-        <v>75.45033175572252</v>
-      </c>
-      <c r="H59">
         <v>0.3081154903114778</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>15126.5151</v>
       </c>
@@ -1949,16 +1769,13 @@
         <v>3258857784.176424</v>
       </c>
       <c r="F60">
-        <v>-9281268.46865187</v>
+        <v>-468.301751026326</v>
       </c>
       <c r="G60">
-        <v>182.3348335479448</v>
-      </c>
-      <c r="H60">
         <v>0.2918447953523169</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>15180.8648</v>
       </c>
@@ -1975,16 +1792,13 @@
         <v>1854800454.515697</v>
       </c>
       <c r="F61">
-        <v>-39080523.23495647</v>
+        <v>-1978.956643148655</v>
       </c>
       <c r="G61">
-        <v>69.11817059749109</v>
-      </c>
-      <c r="H61">
         <v>0.1165125318342395</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>15211.6866</v>
       </c>
@@ -2001,16 +1815,13 @@
         <v>3705141813.06572</v>
       </c>
       <c r="F62">
-        <v>-23251624.81021379</v>
+        <v>-1179.805388572071</v>
       </c>
       <c r="G62">
-        <v>277.8832990826441</v>
-      </c>
-      <c r="H62">
         <v>0.4331408516259484</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>15223.782</v>
       </c>
@@ -2027,16 +1838,13 @@
         <v>3223982704.849172</v>
       </c>
       <c r="F63">
-        <v>-14905797.98844591</v>
+        <v>-756.9333607330423</v>
       </c>
       <c r="G63">
-        <v>387.9398314054862</v>
-      </c>
-      <c r="H63">
         <v>0.3851430895936556</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>15228.8918</v>
       </c>
@@ -2053,16 +1861,13 @@
         <v>2355292363.132841</v>
       </c>
       <c r="F64">
-        <v>-4009330.396214958</v>
+        <v>-203.6665340962377</v>
       </c>
       <c r="G64">
-        <v>157.4861582376646</v>
-      </c>
-      <c r="H64">
         <v>0.1769774117760842</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>15249.1397</v>
       </c>
@@ -2079,16 +1884,13 @@
         <v>3630380395.531632</v>
       </c>
       <c r="F65">
-        <v>-18025201.92779333</v>
+        <v>-916.8647222808471</v>
       </c>
       <c r="G65">
-        <v>334.2137252694796</v>
-      </c>
-      <c r="H65">
         <v>0.3773998264652626</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>15250.6653</v>
       </c>
@@ -2105,16 +1907,13 @@
         <v>1107639082.173041</v>
       </c>
       <c r="F66">
-        <v>-260580081.1625765</v>
+        <v>-13255.90704711361</v>
       </c>
       <c r="G66">
-        <v>102.2198540424131</v>
-      </c>
-      <c r="H66">
         <v>0.09073517366669714</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>15339.5784</v>
       </c>
@@ -2131,16 +1930,13 @@
         <v>3256569347.414473</v>
       </c>
       <c r="F67">
-        <v>20886780.63261012</v>
+        <v>1068.722627518508</v>
       </c>
       <c r="G67">
-        <v>537.452358866126</v>
-      </c>
-      <c r="H67">
         <v>0.4534573490256101</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>15347.9951</v>
       </c>
@@ -2157,16 +1953,13 @@
         <v>2755933012.006021</v>
       </c>
       <c r="F68">
-        <v>-40158856.45263437</v>
+        <v>-2055.949455815494</v>
       </c>
       <c r="G68">
-        <v>101.5716236259524</v>
-      </c>
-      <c r="H68">
         <v>0.2242747228479715</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>15494.572</v>
       </c>
@@ -2183,16 +1976,13 @@
         <v>1496411122.723968</v>
       </c>
       <c r="F69">
-        <v>102506662.6875892</v>
+        <v>5297.9923767012</v>
       </c>
       <c r="G69">
-        <v>243.7876290177686</v>
-      </c>
-      <c r="H69">
         <v>0.07275870586776545</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>15518.5211</v>
       </c>
@@ -2209,16 +1999,13 @@
         <v>1369355575.743196</v>
       </c>
       <c r="F70">
-        <v>99287991.6351856</v>
+        <v>5139.569201274378</v>
       </c>
       <c r="G70">
-        <v>251.1387476538749</v>
-      </c>
-      <c r="H70">
         <v>0.09573122735755857</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>15523.6066</v>
       </c>
@@ -2235,16 +2022,13 @@
         <v>1331376628.093632</v>
       </c>
       <c r="F71">
-        <v>59480893.18530277</v>
+        <v>3079.991187701609</v>
       </c>
       <c r="G71">
-        <v>46.34888772717395</v>
-      </c>
-      <c r="H71">
         <v>0.1113970403173474</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>15536.003</v>
       </c>
@@ -2261,16 +2045,13 @@
         <v>3060273067.410341</v>
       </c>
       <c r="F72">
-        <v>-11301427.42831764</v>
+        <v>-585.6688805480715</v>
       </c>
       <c r="G72">
-        <v>175.5993074487081</v>
-      </c>
-      <c r="H72">
         <v>0.2637201968508752</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>15538.4919</v>
       </c>
@@ -2287,16 +2068,13 @@
         <v>3785816998.200178</v>
       </c>
       <c r="F73">
-        <v>-15407605.52427121</v>
+        <v>-798.5894901084476</v>
       </c>
       <c r="G73">
-        <v>191.0060096595961</v>
-      </c>
-      <c r="H73">
         <v>0.3061096630590966</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>15546.3307</v>
       </c>
@@ -2313,16 +2091,13 @@
         <v>3349839984.879492</v>
       </c>
       <c r="F74">
-        <v>11518568.90202348</v>
+        <v>597.3181511262878</v>
       </c>
       <c r="G74">
-        <v>-7.713523254235525</v>
-      </c>
-      <c r="H74">
         <v>0.2716448587094411</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>15555.6848</v>
       </c>
@@ -2339,16 +2114,13 @@
         <v>2115502168.66674</v>
       </c>
       <c r="F75">
-        <v>-18044504.93170052</v>
+        <v>-936.2974574655801</v>
       </c>
       <c r="G75">
-        <v>304.5009523394917</v>
-      </c>
-      <c r="H75">
         <v>0.1553198299975723</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>15592.5237</v>
       </c>
@@ -2365,16 +2137,13 @@
         <v>3345003900.470722</v>
       </c>
       <c r="F76">
-        <v>7466818.371781709</v>
+        <v>388.3570979805257</v>
       </c>
       <c r="G76">
-        <v>-34.60802334615429</v>
-      </c>
-      <c r="H76">
         <v>0.2849728050222721</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>15603.1385</v>
       </c>
@@ -2391,16 +2160,13 @@
         <v>641019393.6751802</v>
       </c>
       <c r="F77">
-        <v>176514311.1066101</v>
+        <v>9186.9545274752</v>
       </c>
       <c r="G77">
-        <v>265.147676599972</v>
-      </c>
-      <c r="H77">
         <v>0.07101421308044442</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>15615.4038</v>
       </c>
@@ -2417,16 +2183,13 @@
         <v>2128410984.442255</v>
       </c>
       <c r="F78">
-        <v>-29292744.5491517</v>
+        <v>-1525.783588664053</v>
       </c>
       <c r="G78">
-        <v>247.660755848954</v>
-      </c>
-      <c r="H78">
         <v>0.161362117607041</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>15617.8987</v>
       </c>
@@ -2443,16 +2206,13 @@
         <v>1920806518.761335</v>
       </c>
       <c r="F79">
-        <v>-14444204.9751977</v>
+        <v>-752.4812555976291</v>
       </c>
       <c r="G79">
-        <v>99.81629483784745</v>
-      </c>
-      <c r="H79">
         <v>0.1789902725732976</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>15625.9278</v>
       </c>
@@ -2469,16 +2229,13 @@
         <v>3308374422.757637</v>
       </c>
       <c r="F80">
-        <v>-12927320.51711405</v>
+        <v>-673.8048935588527</v>
       </c>
       <c r="G80">
-        <v>368.3630993007404</v>
-      </c>
-      <c r="H80">
         <v>0.4443422233718773</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>15636.2214</v>
       </c>
@@ -2495,16 +2252,13 @@
         <v>3708052043.393218</v>
       </c>
       <c r="F81">
-        <v>-15545737.79064793</v>
+        <v>-810.816876753355</v>
       </c>
       <c r="G81">
-        <v>230.0753746088103</v>
-      </c>
-      <c r="H81">
         <v>0.4284795679818084</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>15652.791</v>
       </c>
@@ -2521,16 +2275,13 @@
         <v>3638577979.461855</v>
       </c>
       <c r="F82">
-        <v>-5329848.285221979</v>
+        <v>-278.2825610507995</v>
       </c>
       <c r="G82">
-        <v>42.13583432360907</v>
-      </c>
-      <c r="H82">
         <v>0.274951494347049</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>15657.151</v>
       </c>
@@ -2547,16 +2298,13 @@
         <v>2776986058.737023</v>
       </c>
       <c r="F83">
-        <v>-5524094.789445193</v>
+        <v>-288.5051387743804</v>
       </c>
       <c r="G83">
-        <v>271.8919236143388</v>
-      </c>
-      <c r="H83">
         <v>0.2204879042854734</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>15666.2978</v>
       </c>
@@ -2573,16 +2321,13 @@
         <v>3431266749.599977</v>
       </c>
       <c r="F84">
-        <v>-6144866.720842819</v>
+        <v>-321.1134628718616</v>
       </c>
       <c r="G84">
-        <v>256.424267459517</v>
-      </c>
-      <c r="H84">
         <v>0.3761397353210935</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>15669.5259</v>
       </c>
@@ -2599,16 +2344,13 @@
         <v>2161430199.950818</v>
       </c>
       <c r="F85">
-        <v>-39521753.0038707</v>
+        <v>-2065.719888685336</v>
       </c>
       <c r="G85">
-        <v>53.57015187109182</v>
-      </c>
-      <c r="H85">
         <v>0.1846932014278642</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>15680.8729</v>
       </c>
@@ -2625,16 +2367,13 @@
         <v>2958394824.958137</v>
       </c>
       <c r="F86">
-        <v>130391513.3155631</v>
+        <v>6820.228133178801</v>
       </c>
       <c r="G86">
-        <v>30.58936425919826</v>
-      </c>
-      <c r="H86">
         <v>0.1095352302109741</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>15681.8073</v>
       </c>
@@ -2651,16 +2390,13 @@
         <v>3358313621.082551</v>
       </c>
       <c r="F87">
-        <v>-940112.4217698813</v>
+        <v>-49.17627266722034</v>
       </c>
       <c r="G87">
-        <v>281.0230382164584</v>
-      </c>
-      <c r="H87">
         <v>0.2959690392144889</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>15686.8036</v>
       </c>
@@ -2677,16 +2413,13 @@
         <v>1497438084.829989</v>
       </c>
       <c r="F88">
-        <v>-13984483.06792466</v>
+        <v>-731.7464466790732</v>
       </c>
       <c r="G88">
-        <v>309.6002183101011</v>
-      </c>
-      <c r="H88">
         <v>0.1346798386803697</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>15690.7319</v>
       </c>
@@ -2703,16 +2436,13 @@
         <v>3691882257.913296</v>
       </c>
       <c r="F89">
-        <v>70925485.27770038</v>
+        <v>3712.144544671667</v>
       </c>
       <c r="G89">
-        <v>43.94458190379509</v>
-      </c>
-      <c r="H89">
         <v>0.2996072714044568</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>15696.1452</v>
       </c>
@@ -2729,16 +2459,13 @@
         <v>3389258173.328023</v>
       </c>
       <c r="F90">
-        <v>-13139329.48703831</v>
+        <v>-687.9328531675499</v>
       </c>
       <c r="G90">
-        <v>374.3551108861444</v>
-      </c>
-      <c r="H90">
         <v>0.3678593444319519</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>15727.8899</v>
       </c>
@@ -2755,16 +2482,13 @@
         <v>3360735596.695724</v>
       </c>
       <c r="F91">
-        <v>-1424466.953564628</v>
+        <v>-74.73129318139807</v>
       </c>
       <c r="G91">
-        <v>249.7017225159084</v>
-      </c>
-      <c r="H91">
         <v>0.4054824924645283</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>15778.3807</v>
       </c>
@@ -2781,16 +2505,13 @@
         <v>2775194890.509315</v>
       </c>
       <c r="F92">
-        <v>-46096031.02674194</v>
+        <v>-2426.081599418714</v>
       </c>
       <c r="G92">
-        <v>98.80106273223207</v>
-      </c>
-      <c r="H92">
         <v>0.3723288103306039</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>15793.3148</v>
       </c>
@@ -2807,16 +2528,13 @@
         <v>3272568222.625025</v>
       </c>
       <c r="F93">
-        <v>-1256206.585799897</v>
+        <v>-66.17807424796388</v>
       </c>
       <c r="G93">
-        <v>324.5962672596718</v>
-      </c>
-      <c r="H93">
         <v>0.3233172122556545</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>15820.9574</v>
       </c>
@@ -2833,16 +2551,13 @@
         <v>1984738847.859315</v>
       </c>
       <c r="F94">
-        <v>-3376419.004386254</v>
+        <v>-178.1839325923471</v>
       </c>
       <c r="G94">
-        <v>100.4300806716848</v>
-      </c>
-      <c r="H94">
         <v>0.1612902026675819</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>15822.4644</v>
       </c>
@@ -2859,16 +2574,13 @@
         <v>2977581355.170902</v>
       </c>
       <c r="F95">
-        <v>-4201763.757616004</v>
+        <v>-221.7612475451792</v>
       </c>
       <c r="G95">
-        <v>414.9451478422461</v>
-      </c>
-      <c r="H95">
         <v>0.4415645291109971</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>15823.4608</v>
       </c>
@@ -2885,16 +2597,13 @@
         <v>2551710361.498037</v>
       </c>
       <c r="F96">
-        <v>25374146.47156611</v>
+        <v>1339.283495723884</v>
       </c>
       <c r="G96">
-        <v>208.4068130961335</v>
-      </c>
-      <c r="H96">
         <v>0.2550195298247916</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>15826.0352</v>
       </c>
@@ -2911,16 +2620,13 @@
         <v>2189644938.355878</v>
       </c>
       <c r="F97">
-        <v>17936058.31621805</v>
+        <v>946.8445449680066</v>
       </c>
       <c r="G97">
-        <v>172.3812270593169</v>
-      </c>
-      <c r="H97">
         <v>0.181240817154657</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>15827.1448</v>
       </c>
@@ -2937,16 +2643,13 @@
         <v>4022960594.522149</v>
       </c>
       <c r="F98">
-        <v>12832525.2108562</v>
+        <v>677.4766407529892</v>
       </c>
       <c r="G98">
-        <v>225.4058009455241</v>
-      </c>
-      <c r="H98">
         <v>0.3619750833147793</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>15839.4915</v>
       </c>
@@ -2963,16 +2666,13 @@
         <v>3121919735.65976</v>
       </c>
       <c r="F99">
-        <v>2315641.968682407</v>
+        <v>122.3467872451452</v>
       </c>
       <c r="G99">
-        <v>431.5333003021923</v>
-      </c>
-      <c r="H99">
         <v>0.3784642904295059</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>15857.6516</v>
       </c>
@@ -2989,16 +2689,13 @@
         <v>1731865508.150192</v>
       </c>
       <c r="F100">
-        <v>-73051761.23565413</v>
+        <v>-3864.10449907504</v>
       </c>
       <c r="G100">
-        <v>1.890522443555685</v>
-      </c>
-      <c r="H100">
         <v>0.1399407860587148</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>15868.0489</v>
       </c>
@@ -3015,16 +2712,13 @@
         <v>3139864006.512664</v>
       </c>
       <c r="F101">
-        <v>-26694836.80401955</v>
+        <v>-1412.962449025602</v>
       </c>
       <c r="G101">
-        <v>360.8531826447532</v>
-      </c>
-      <c r="H101">
         <v>0.2671023876389835</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>15872.8622</v>
       </c>
@@ -3041,16 +2735,13 @@
         <v>3555038684.349282</v>
       </c>
       <c r="F102">
-        <v>-11382656.53319679</v>
+        <v>-602.668722966512</v>
       </c>
       <c r="G102">
-        <v>330.5243848898632</v>
-      </c>
-      <c r="H102">
         <v>0.3705940902464075</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>15882.7876</v>
       </c>
@@ -3067,16 +2758,13 @@
         <v>3312740761.39504</v>
       </c>
       <c r="F103">
-        <v>7834604.476762424</v>
+        <v>415.0719087767916</v>
       </c>
       <c r="G103">
-        <v>166.1026827974451</v>
-      </c>
-      <c r="H103">
         <v>0.2843355863178736</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>15899.5732</v>
       </c>
@@ -3093,16 +2781,13 @@
         <v>3151944383.743469</v>
       </c>
       <c r="F104">
-        <v>7595046.538135923</v>
+        <v>402.8057655283258</v>
       </c>
       <c r="G104">
-        <v>328.0835720292703</v>
-      </c>
-      <c r="H104">
         <v>0.3262042948627143</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>15905.8653</v>
       </c>
@@ -3119,16 +2804,13 @@
         <v>2723534864.191213</v>
       </c>
       <c r="F105">
-        <v>-9337295.743194398</v>
+        <v>-495.4020872720379</v>
       </c>
       <c r="G105">
-        <v>82.93084284040249</v>
-      </c>
-      <c r="H105">
         <v>0.2033618662005523</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>15910.3901</v>
       </c>
@@ -3145,16 +2827,13 @@
         <v>3508808338.613146</v>
       </c>
       <c r="F106">
-        <v>-34674361.21255974</v>
+        <v>-1840.216702178955</v>
       </c>
       <c r="G106">
-        <v>258.1430529977978</v>
-      </c>
-      <c r="H106">
         <v>0.3531457441222818</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>15915.6521</v>
       </c>
@@ -3171,16 +2850,13 @@
         <v>3318848889.865634</v>
       </c>
       <c r="F107">
-        <v>-19919719.44406146</v>
+        <v>-1057.516829238702</v>
       </c>
       <c r="G107">
-        <v>231.6868458079414</v>
-      </c>
-      <c r="H107">
         <v>0.3210528996917547</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>15975.6174</v>
       </c>
@@ -3197,16 +2873,13 @@
         <v>1720394457.41666</v>
       </c>
       <c r="F108">
-        <v>-73252353.96180697</v>
+        <v>-3903.539022877941</v>
       </c>
       <c r="G108">
-        <v>-5.629687746690727</v>
-      </c>
-      <c r="H108">
         <v>0.1261742097771656</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>15985.0942</v>
       </c>
@@ -3223,16 +2896,13 @@
         <v>3133499126.051802</v>
       </c>
       <c r="F109">
-        <v>-26487956.92375318</v>
+        <v>-1412.354450763923</v>
       </c>
       <c r="G109">
-        <v>513.8733151715904</v>
-      </c>
-      <c r="H109">
         <v>0.4158214756267831</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>16002.0995</v>
       </c>
@@ -3249,16 +2919,13 @@
         <v>2558647282.837667</v>
       </c>
       <c r="F110">
-        <v>-8682077.774653837</v>
+        <v>-463.4256595059296</v>
       </c>
       <c r="G110">
-        <v>97.41976553934342</v>
-      </c>
-      <c r="H110">
         <v>0.204670223380907</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>16013.9898</v>
       </c>
@@ -3275,16 +2942,13 @@
         <v>3626362545.983729</v>
       </c>
       <c r="F111">
-        <v>-21895157.18864502</v>
+        <v>-1169.572024582766</v>
       </c>
       <c r="G111">
-        <v>41.18545194646949</v>
-      </c>
-      <c r="H111">
         <v>0.3337429393805633</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>16033.8018</v>
       </c>
@@ -3301,16 +2965,13 @@
         <v>1277680401.84855</v>
       </c>
       <c r="F112">
-        <v>-51875006.56585878</v>
+        <v>-2774.433808557566</v>
       </c>
       <c r="G112">
-        <v>272.9839087463706</v>
-      </c>
-      <c r="H112">
         <v>0.1093389375896945</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>16045.0391</v>
       </c>
@@ -3327,16 +2988,13 @@
         <v>3492410645.778711</v>
       </c>
       <c r="F113">
-        <v>-7629008.36744724</v>
+        <v>-408.3085548586895</v>
       </c>
       <c r="G113">
-        <v>214.870979469381</v>
-      </c>
-      <c r="H113">
         <v>0.3703739027245262</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>16075.7929</v>
       </c>
@@ -3353,16 +3011,13 @@
         <v>2869088868.426933</v>
       </c>
       <c r="F114">
-        <v>21402897.52163912</v>
+        <v>1147.690259917362</v>
       </c>
       <c r="G114">
-        <v>292.7844131468875</v>
-      </c>
-      <c r="H114">
         <v>0.2547680026496776</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>16080.3141</v>
       </c>
@@ -3379,16 +3034,13 @@
         <v>2928469922.12919</v>
       </c>
       <c r="F115">
-        <v>-14639445.61954908</v>
+        <v>-785.233193612318</v>
       </c>
       <c r="G115">
-        <v>134.2328068970648</v>
-      </c>
-      <c r="H115">
         <v>0.2850064315843686</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>16093.1316</v>
       </c>
@@ -3405,16 +3057,13 @@
         <v>5881421966.728233</v>
       </c>
       <c r="F116">
-        <v>42492104.45779014</v>
+        <v>2281.01373570442</v>
       </c>
       <c r="G116">
-        <v>-137.8516154967916</v>
-      </c>
-      <c r="H116">
         <v>0.2468524416413167</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>16160.9789</v>
       </c>
@@ -3431,16 +3080,13 @@
         <v>2618658247.111792</v>
       </c>
       <c r="F117">
-        <v>19895462.42167929</v>
+        <v>1072.509501947148</v>
       </c>
       <c r="G117">
-        <v>103.8821828568387</v>
-      </c>
-      <c r="H117">
         <v>0.2127408609809779</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>16179.3972</v>
       </c>
@@ -3457,16 +3103,13 @@
         <v>2829358146.408769</v>
       </c>
       <c r="F118">
-        <v>36547100.96472555</v>
+        <v>1972.400389960532</v>
       </c>
       <c r="G118">
-        <v>353.9091028653904</v>
-      </c>
-      <c r="H118">
         <v>0.2668194343188615</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>16185.3311</v>
       </c>
@@ -3483,16 +3126,13 @@
         <v>3133390673.07931</v>
       </c>
       <c r="F119">
-        <v>4532024.68046705</v>
+        <v>244.6772731353124</v>
       </c>
       <c r="G119">
-        <v>331.5523769479758</v>
-      </c>
-      <c r="H119">
         <v>0.2910501553658875</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>16199.487</v>
       </c>
@@ -3509,16 +3149,13 @@
         <v>2764932351.493311</v>
       </c>
       <c r="F120">
-        <v>-16619189.83752748</v>
+        <v>-898.0301204861215</v>
       </c>
       <c r="G120">
-        <v>342.3664263381521</v>
-      </c>
-      <c r="H120">
         <v>0.2633273589903313</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>16202.9307</v>
       </c>
@@ -3535,16 +3172,13 @@
         <v>4044677549.196068</v>
       </c>
       <c r="F121">
-        <v>-15095353.39127744</v>
+        <v>-815.8611892445713</v>
       </c>
       <c r="G121">
-        <v>81.41038431483929</v>
-      </c>
-      <c r="H121">
         <v>0.3383293092022073</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>16208.6822</v>
       </c>
@@ -3561,16 +3195,13 @@
         <v>2093577827.286536</v>
       </c>
       <c r="F122">
-        <v>39141542.31144371</v>
+        <v>2116.240748964259</v>
       </c>
       <c r="G122">
-        <v>92.47897340587421</v>
-      </c>
-      <c r="H122">
         <v>0.2721761137192119</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>16212.1746</v>
       </c>
@@ -3587,16 +3218,13 @@
         <v>3179222056.615446</v>
       </c>
       <c r="F123">
-        <v>-28992438.82611369</v>
+        <v>-1567.854969081568</v>
       </c>
       <c r="G123">
-        <v>392.0263793176198</v>
-      </c>
-      <c r="H123">
         <v>0.3465751080497704</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>16230.0565</v>
       </c>
@@ -3613,16 +3241,13 @@
         <v>2576563446.582314</v>
       </c>
       <c r="F124">
-        <v>-4456211.232154349</v>
+        <v>-241.2490215689616</v>
       </c>
       <c r="G124">
-        <v>319.5558514401135</v>
-      </c>
-      <c r="H124">
         <v>0.2279091477755157</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>16236.0883</v>
       </c>
@@ -3639,16 +3264,13 @@
         <v>3095424452.912705</v>
       </c>
       <c r="F125">
-        <v>-15887395.34195823</v>
+        <v>-860.4267566733614</v>
       </c>
       <c r="G125">
-        <v>347.1339959839592</v>
-      </c>
-      <c r="H125">
         <v>0.3331174967952071</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>16240.4048</v>
       </c>
@@ -3665,16 +3287,13 @@
         <v>2524462559.141798</v>
       </c>
       <c r="F126">
-        <v>20463206.05191058</v>
+        <v>1108.536870867478</v>
       </c>
       <c r="G126">
-        <v>219.6700325181319</v>
-      </c>
-      <c r="H126">
         <v>0.2409366930462681</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>16250.9009</v>
       </c>
@@ -3691,16 +3310,13 @@
         <v>2387424251.933375</v>
       </c>
       <c r="F127">
-        <v>21318329.71836824</v>
+        <v>1155.607373065873</v>
       </c>
       <c r="G127">
-        <v>269.3370609356932</v>
-      </c>
-      <c r="H127">
         <v>0.1971182439221921</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>16289.221</v>
       </c>
@@ -3717,16 +3333,13 @@
         <v>2701662462.370373</v>
       </c>
       <c r="F128">
-        <v>22456878.06023574</v>
+        <v>1220.196057047499</v>
       </c>
       <c r="G128">
-        <v>430.6616944641905</v>
-      </c>
-      <c r="H128">
         <v>0.2421817934605625</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>16297.2992</v>
       </c>
@@ -3743,16 +3356,13 @@
         <v>2373912766.56643</v>
       </c>
       <c r="F129">
-        <v>6287354.073957154</v>
+        <v>341.7928023786296</v>
       </c>
       <c r="G129">
-        <v>40.46949130141842</v>
-      </c>
-      <c r="H129">
         <v>0.193477939367108</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>16320.783</v>
       </c>
@@ -3769,16 +3379,13 @@
         <v>2288132164.547809</v>
       </c>
       <c r="F130">
-        <v>51227219.09015395</v>
+        <v>2788.828362048972</v>
       </c>
       <c r="G130">
-        <v>495.9563745355763</v>
-      </c>
-      <c r="H130">
         <v>0.4410555585752565</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>16323.1594</v>
       </c>
@@ -3795,16 +3402,13 @@
         <v>2344624347.877722</v>
       </c>
       <c r="F131">
-        <v>3006011.11654563</v>
+        <v>163.671995631264</v>
       </c>
       <c r="G131">
-        <v>191.0072361620598</v>
-      </c>
-      <c r="H131">
         <v>0.203581244422123</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>16335.9908</v>
       </c>
@@ -3821,16 +3425,13 @@
         <v>2324035744.369361</v>
       </c>
       <c r="F132">
-        <v>-39089639.85088311</v>
+        <v>-2130.033822127105</v>
       </c>
       <c r="G132">
-        <v>36.7033088949083</v>
-      </c>
-      <c r="H132">
         <v>0.1818702219900509</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>16388.6201</v>
       </c>
@@ -3847,16 +3448,13 @@
         <v>1935730441.132565</v>
       </c>
       <c r="F133">
-        <v>120891807.0093691</v>
+        <v>6608.742893877828</v>
       </c>
       <c r="G133">
-        <v>208.5370214600775</v>
-      </c>
-      <c r="H133">
         <v>0.1580072208661591</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>16398.8704</v>
       </c>
@@ -3873,16 +3471,13 @@
         <v>3128094910.877211</v>
       </c>
       <c r="F134">
-        <v>-12752656.47561182</v>
+        <v>-697.5801248142121</v>
       </c>
       <c r="G134">
-        <v>142.5940394123858</v>
-      </c>
-      <c r="H134">
         <v>0.3533060889647369</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>16409.0824</v>
       </c>
@@ -3899,16 +3494,13 @@
         <v>2985467084.742025</v>
       </c>
       <c r="F135">
-        <v>-7865713.081280822</v>
+        <v>-430.5287510669968</v>
       </c>
       <c r="G135">
-        <v>321.5504153084832</v>
-      </c>
-      <c r="H135">
         <v>0.3185623719321544</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>16441.1165</v>
       </c>
@@ -3925,16 +3517,13 @@
         <v>2539554703.956648</v>
       </c>
       <c r="F136">
-        <v>-28550976.2097047</v>
+        <v>-1565.783667828661</v>
       </c>
       <c r="G136">
-        <v>133.1104821214017</v>
-      </c>
-      <c r="H136">
         <v>0.2267783788539568</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>16444.8936</v>
       </c>
@@ -3951,16 +3540,13 @@
         <v>2122137809.853559</v>
       </c>
       <c r="F137">
-        <v>65936362.86466946</v>
+        <v>3616.894210814075</v>
       </c>
       <c r="G137">
-        <v>313.5581417605769</v>
-      </c>
-      <c r="H137">
         <v>0.1840338273925146</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>16449.311</v>
       </c>
@@ -3977,16 +3563,13 @@
         <v>3267782809.83175</v>
       </c>
       <c r="F138">
-        <v>-32685213.94314819</v>
+        <v>-1793.407143157262</v>
       </c>
       <c r="G138">
-        <v>382.7298065708976</v>
-      </c>
-      <c r="H138">
         <v>0.4274566662816801</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>16491.1731</v>
       </c>
@@ -4003,16 +3586,13 @@
         <v>2910109884.384812</v>
       </c>
       <c r="F139">
-        <v>-11321095.68117637</v>
+        <v>-622.7588849813882</v>
       </c>
       <c r="G139">
-        <v>430.8414697035229</v>
-      </c>
-      <c r="H139">
         <v>0.451917408463142</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>16521.7407</v>
       </c>
@@ -4029,16 +3609,13 @@
         <v>3265067322.629371</v>
       </c>
       <c r="F140">
-        <v>2226455.036940136</v>
+        <v>122.7014160269456</v>
       </c>
       <c r="G140">
-        <v>377.4228902383945</v>
-      </c>
-      <c r="H140">
         <v>0.3644826634808077</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>16543.7138</v>
       </c>
@@ -4055,16 +3632,13 @@
         <v>2365213727.85796</v>
       </c>
       <c r="F141">
-        <v>-30673859.85569298</v>
+        <v>-1692.704726825955</v>
       </c>
       <c r="G141">
-        <v>326.1821565130869</v>
-      </c>
-      <c r="H141">
         <v>0.1880430798961218</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>16556.5189</v>
       </c>
@@ -4081,16 +3655,13 @@
         <v>2429909011.294053</v>
       </c>
       <c r="F142">
-        <v>16523722.63063598</v>
+        <v>912.5502955910562</v>
       </c>
       <c r="G142">
-        <v>405.6016304391342</v>
-      </c>
-      <c r="H142">
         <v>0.2244873897585358</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>16566.2943</v>
       </c>
@@ -4107,16 +3678,13 @@
         <v>3024902844.993293</v>
       </c>
       <c r="F143">
-        <v>-26526815.54057986</v>
+        <v>-1465.853525722143</v>
       </c>
       <c r="G143">
-        <v>544.7055824357349</v>
-      </c>
-      <c r="H143">
         <v>0.3370203912934385</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>16650.4242</v>
       </c>
@@ -4133,16 +3701,13 @@
         <v>2935604332.999224</v>
       </c>
       <c r="F144">
-        <v>9043179.713305684</v>
+        <v>502.2568433385168</v>
       </c>
       <c r="G144">
-        <v>70.21986776515132</v>
-      </c>
-      <c r="H144">
         <v>0.2640166078161914</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>16670.0368</v>
       </c>
@@ -4159,16 +3724,13 @@
         <v>2969276017.595953</v>
       </c>
       <c r="F145">
-        <v>-45951324.73962834</v>
+        <v>-2555.136252617463</v>
       </c>
       <c r="G145">
-        <v>118.6938124995394</v>
-      </c>
-      <c r="H145">
         <v>0.2605377600770622</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>16727.8488</v>
       </c>
@@ -4185,16 +3747,13 @@
         <v>2397325331.73465</v>
       </c>
       <c r="F146">
-        <v>35583227.94198732</v>
+        <v>1985.477015387888</v>
       </c>
       <c r="G146">
-        <v>89.6087900242761</v>
-      </c>
-      <c r="H146">
         <v>0.224178153976504</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>16730.0121</v>
       </c>
@@ -4211,16 +3770,13 @@
         <v>505954929.6191821</v>
       </c>
       <c r="F147">
-        <v>315653138.2201879</v>
+        <v>17615.12907041444</v>
       </c>
       <c r="G147">
-        <v>114.684419813436</v>
-      </c>
-      <c r="H147">
         <v>0.0512515292253517</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>16757.6467</v>
       </c>
@@ -4237,16 +3793,13 @@
         <v>2634097295.423865</v>
       </c>
       <c r="F148">
-        <v>-14186611.91552306</v>
+        <v>-792.9968720339745</v>
       </c>
       <c r="G148">
-        <v>316.651054994061</v>
-      </c>
-      <c r="H148">
         <v>0.2543007274486686</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>16804.2402</v>
       </c>
@@ -4263,16 +3816,13 @@
         <v>2153922306.858066</v>
       </c>
       <c r="F149">
-        <v>104028839.900463</v>
+        <v>5831.121744933408</v>
       </c>
       <c r="G149">
-        <v>121.3139475424352</v>
-      </c>
-      <c r="H149">
         <v>0.2022607452821291</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>16974.5482</v>
       </c>
@@ -4289,16 +3839,13 @@
         <v>2738149516.287169</v>
       </c>
       <c r="F150">
-        <v>5315605.952762325</v>
+        <v>300.9750653567863</v>
       </c>
       <c r="G150">
-        <v>150.1209848485497</v>
-      </c>
-      <c r="H150">
         <v>0.275049646207114</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>17015.7476</v>
       </c>
@@ -4315,16 +3862,13 @@
         <v>3196825565.453818</v>
       </c>
       <c r="F151">
-        <v>-39561255.61846042</v>
+        <v>-2245.435293245307</v>
       </c>
       <c r="G151">
-        <v>100.4256205295912</v>
-      </c>
-      <c r="H151">
         <v>0.2911184933888755</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>17042.4469</v>
       </c>
@@ -4341,16 +3885,13 @@
         <v>1499806598.330992</v>
       </c>
       <c r="F152">
-        <v>-27980409.52283004</v>
+        <v>-1590.616166442569</v>
       </c>
       <c r="G152">
-        <v>54.53187711609101</v>
-      </c>
-      <c r="H152">
         <v>0.1307356644316816</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>17165.7965</v>
       </c>
@@ -4367,16 +3908,13 @@
         <v>2868653579.087183</v>
       </c>
       <c r="F153">
-        <v>-9407379.650744831</v>
+        <v>-538.656770077085</v>
       </c>
       <c r="G153">
-        <v>134.4768316275478</v>
-      </c>
-      <c r="H153">
         <v>0.248327186007527</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>17209.0026</v>
       </c>
@@ -4393,16 +3931,13 @@
         <v>2297603256.137409</v>
       </c>
       <c r="F154">
-        <v>-55151778.96647949</v>
+        <v>-3165.881419062616</v>
       </c>
       <c r="G154">
-        <v>83.61924462412458</v>
-      </c>
-      <c r="H154">
         <v>0.2735108696719739</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>17307.0446</v>
       </c>
@@ -4419,16 +3954,13 @@
         <v>3115670104.780177</v>
       </c>
       <c r="F155">
-        <v>20684258.06144327</v>
+        <v>1194.10438431477</v>
       </c>
       <c r="G155">
-        <v>93.53874735469434</v>
-      </c>
-      <c r="H155">
         <v>0.2996864325395471</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>17315.5826</v>
       </c>
@@ -4445,16 +3977,13 @@
         <v>2184124492.427251</v>
       </c>
       <c r="F156">
-        <v>-59042938.8992428</v>
+        <v>-3410.23590240709</v>
       </c>
       <c r="G156">
-        <v>34.6268981373526</v>
-      </c>
-      <c r="H156">
         <v>0.07181799408757084</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>17688.7397</v>
       </c>
@@ -4471,12 +4000,9 @@
         <v>2313138605.45255</v>
       </c>
       <c r="F157">
-        <v>-12747770.98337865</v>
+        <v>-752.1606391295085</v>
       </c>
       <c r="G157">
-        <v>111.8581796353327</v>
-      </c>
-      <c r="H157">
         <v>0.2712122151904077</v>
       </c>
     </row>
